--- a/app1/Excelfiles/didijiju.xlsx
+++ b/app1/Excelfiles/didijiju.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>560u</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -494,13 +494,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
